--- a/artfynd/A 53249-2023 artfynd.xlsx
+++ b/artfynd/A 53249-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 53249-2023 artfynd.xlsx
+++ b/artfynd/A 53249-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>113887244</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -786,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113888082</v>
+        <v>113887435</v>
       </c>
       <c r="B3" t="n">
-        <v>78246</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484560</v>
+        <v>484577</v>
       </c>
       <c r="R3" t="n">
-        <v>6859274</v>
+        <v>6859227</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113887052</v>
+        <v>113888082</v>
       </c>
       <c r="B4" t="n">
-        <v>79074</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +898,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -944,7 +929,7 @@
         <v>484560</v>
       </c>
       <c r="R4" t="n">
-        <v>6859267</v>
+        <v>6859274</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1008,15 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113887435</v>
+        <v>113887052</v>
       </c>
       <c r="B5" t="n">
-        <v>91628</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1024,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484577</v>
+        <v>484560</v>
       </c>
       <c r="R5" t="n">
-        <v>6859227</v>
+        <v>6859267</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>

--- a/artfynd/A 53249-2023 artfynd.xlsx
+++ b/artfynd/A 53249-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887244</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887435</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113888082</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,8 +1116,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113887052</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>